--- a/Configs/GameConfig/Datas/fg/#NarrativeEntry-资料库条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#NarrativeEntry-资料库条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,7 +1456,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>terminal.foundry.a</t>
+          <t>terminal.silent.d</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>terminal:terminal.lore.foundry.a</t>
+          <t>terminal:terminal.lore.silent.d</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>narrative.title.terminal.lore.foundry.a</t>
+          <t>narrative.title.terminal.lore.silent.d</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>terminal.lore.foundry.a</t>
+          <t>terminal.lore.silent.d</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1496,7 +1496,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>terminal.foundry.b</t>
+          <t>terminal.silent.e</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1512,17 +1512,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>terminal:terminal.lore.foundry.b</t>
+          <t>terminal:terminal.lore.silent.e</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>narrative.title.terminal.lore.foundry.b</t>
+          <t>narrative.title.terminal.lore.silent.e</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>terminal.lore.foundry.b</t>
+          <t>terminal.lore.silent.e</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1536,7 +1536,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>terminal.foundry.c</t>
+          <t>terminal.foundry.a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>terminal:terminal.lore.foundry.c</t>
+          <t>terminal:terminal.lore.foundry.a</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>narrative.title.terminal.lore.foundry.c</t>
+          <t>narrative.title.terminal.lore.foundry.a</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>terminal.lore.foundry.c</t>
+          <t>terminal.lore.foundry.a</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1576,7 +1576,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>terminal.clarity.a</t>
+          <t>terminal.foundry.b</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1585,24 +1585,24 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>terminal:terminal.lore.clarity.a</t>
+          <t>terminal:terminal.lore.foundry.b</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>narrative.title.terminal.lore.clarity.a</t>
+          <t>narrative.title.terminal.lore.foundry.b</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>terminal.lore.clarity.a</t>
+          <t>terminal.lore.foundry.b</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1616,7 +1616,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>terminal.clarity.b</t>
+          <t>terminal.foundry.c</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1625,24 +1625,24 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>terminal:terminal.lore.clarity.b</t>
+          <t>terminal:terminal.lore.foundry.c</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>narrative.title.terminal.lore.clarity.b</t>
+          <t>narrative.title.terminal.lore.foundry.c</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>terminal.lore.clarity.b</t>
+          <t>terminal.lore.foundry.c</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1656,7 +1656,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>terminal.overclock.a</t>
+          <t>terminal.clarity.a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>terminal:terminal.lore.overclock.a</t>
+          <t>terminal:terminal.lore.clarity.a</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>narrative.title.terminal.lore.overclock.a</t>
+          <t>narrative.title.terminal.lore.clarity.a</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>terminal.lore.overclock.a</t>
+          <t>terminal.lore.clarity.a</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1696,7 +1696,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>terminal.overclock.b</t>
+          <t>terminal.clarity.b</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>terminal:terminal.lore.overclock.b</t>
+          <t>terminal:terminal.lore.clarity.b</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>narrative.title.terminal.lore.overclock.b</t>
+          <t>narrative.title.terminal.lore.clarity.b</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>terminal.lore.overclock.b</t>
+          <t>terminal.lore.clarity.b</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -1736,7 +1736,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>relic.r1.a</t>
+          <t>terminal.overclock.a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1745,24 +1745,24 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r1.a</t>
+          <t>terminal:terminal.lore.overclock.a</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r1.a</t>
+          <t>narrative.title.terminal.lore.overclock.a</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>relic.lore.r1.a</t>
+          <t>terminal.lore.overclock.a</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -1776,7 +1776,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>relic.r1.b</t>
+          <t>terminal.overclock.b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1785,24 +1785,24 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r1.b</t>
+          <t>terminal:terminal.lore.overclock.b</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r1.b</t>
+          <t>narrative.title.terminal.lore.overclock.b</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>relic.lore.r1.b</t>
+          <t>terminal.lore.overclock.b</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -1816,7 +1816,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>relic.r1.c</t>
+          <t>relic.r1.a</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r1.c</t>
+          <t>terminal:relic.lore.r1.a</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r1.c</t>
+          <t>narrative.title.relic.lore.r1.a</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>relic.lore.r1.c</t>
+          <t>relic.lore.r1.a</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -1856,7 +1856,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>relic.r2.a</t>
+          <t>relic.r1.b</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r2.a</t>
+          <t>terminal:relic.lore.r1.b</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r2.a</t>
+          <t>narrative.title.relic.lore.r1.b</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>relic.lore.r2.a</t>
+          <t>relic.lore.r1.b</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -1896,7 +1896,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>relic.r2.b</t>
+          <t>relic.r1.c</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r2.b</t>
+          <t>terminal:relic.lore.r1.c</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r2.b</t>
+          <t>narrative.title.relic.lore.r1.c</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>relic.lore.r2.b</t>
+          <t>relic.lore.r1.c</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -1936,7 +1936,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>relic.r2.c</t>
+          <t>relic.r2.a</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1952,17 +1952,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r2.c</t>
+          <t>terminal:relic.lore.r2.a</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r2.c</t>
+          <t>narrative.title.relic.lore.r2.a</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>relic.lore.r2.c</t>
+          <t>relic.lore.r2.a</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -1976,7 +1976,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>relic.r3.a</t>
+          <t>relic.r2.b</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1992,17 +1992,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r3.a</t>
+          <t>terminal:relic.lore.r2.b</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r3.a</t>
+          <t>narrative.title.relic.lore.r2.b</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>relic.lore.r3.a</t>
+          <t>relic.lore.r2.b</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2016,7 +2016,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>relic.r3.b</t>
+          <t>relic.r2.c</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r3.b</t>
+          <t>terminal:relic.lore.r2.c</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r3.b</t>
+          <t>narrative.title.relic.lore.r2.c</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>relic.lore.r3.b</t>
+          <t>relic.lore.r2.c</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2056,7 +2056,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>relic.r3.c</t>
+          <t>relic.r3.a</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2072,17 +2072,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r3.c</t>
+          <t>terminal:relic.lore.r3.a</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r3.c</t>
+          <t>narrative.title.relic.lore.r3.a</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>relic.lore.r3.c</t>
+          <t>relic.lore.r3.a</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2096,7 +2096,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>relic.r4.a</t>
+          <t>relic.r3.b</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r4.a</t>
+          <t>terminal:relic.lore.r3.b</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r4.a</t>
+          <t>narrative.title.relic.lore.r3.b</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>relic.lore.r4.a</t>
+          <t>relic.lore.r3.b</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2136,7 +2136,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>relic.r4.b</t>
+          <t>relic.r3.c</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2152,17 +2152,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r4.b</t>
+          <t>terminal:relic.lore.r3.c</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r4.b</t>
+          <t>narrative.title.relic.lore.r3.c</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>relic.lore.r4.b</t>
+          <t>relic.lore.r3.c</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2176,7 +2176,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>relic.r4.c</t>
+          <t>relic.r4.a</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>terminal:relic.lore.r4.c</t>
+          <t>terminal:relic.lore.r4.a</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>narrative.title.relic.lore.r4.c</t>
+          <t>narrative.title.relic.lore.r4.a</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>relic.lore.r4.c</t>
+          <t>relic.lore.r4.a</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2210,6 +2210,126 @@
       </c>
       <c r="J44" t="n">
         <v>135</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>relic.r4.b</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>terminal</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>terminal:relic.lore.r4.b</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>narrative.title.relic.lore.r4.b</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>relic.lore.r4.b</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>relic.r4.c</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>terminal</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>terminal:relic.lore.r4.c</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>narrative.title.relic.lore.r4.c</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>relic.lore.r4.c</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>poi.rh_sky_wall</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>terminal</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>terminal:interior.poi.sky_wall.body</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>interior.poi.sky_wall.name</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>interior.poi.sky_wall.body</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
